--- a/hall/resources/sample/SeasonGemDrop.xlsx
+++ b/hall/resources/sample/SeasonGemDrop.xlsx
@@ -77,16 +77,16 @@
     <t>进阶赛季</t>
   </si>
   <si>
-    <t>金蛇赛季</t>
-  </si>
-  <si>
-    <t>金钱赛季</t>
-  </si>
-  <si>
-    <t>赛博赛季</t>
-  </si>
-  <si>
-    <t>体育赛季</t>
+    <t>恶魔之子赛季</t>
+  </si>
+  <si>
+    <t>雪国狂欢赛季</t>
+  </si>
+  <si>
+    <t>愤怒风暴赛季</t>
+  </si>
+  <si>
+    <t>宝石觉醒赛季</t>
   </si>
 </sst>
 </file>
@@ -1243,8 +1243,9 @@
   <dimension ref="A1:F10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
+    <col min="3" max="3" width="15.875" customWidth="1"/>
     <col min="4" max="4" width="17.625" customWidth="1"/>
-    <col min="5" max="5" width="15.125" customWidth="1"/>
+    <col min="5" max="5" width="31.375" customWidth="1"/>
     <col min="6" max="6" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
